--- a/important_mails_2026-05-22.xlsx
+++ b/important_mails_2026-05-22.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -601,21 +601,69 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Fri, 22 May 2026 08:56:06 +0000</t>
+          <t>Fri, 22 May 2026 17:10:56 +0000</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
+          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5月27日前入库助力Prime Day成功</t>
+          <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>¡Buenos días!
+Espero que te encuentres bien.
+Mi nombre es Luana Camargo y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
+Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
+Sobre Worten.
+Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
+En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
+Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
+Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
+Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
+Worten Marketplace tiene una estrategia B2C, c</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 22 May 2026 08:56:06 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5月27日前入库助力Prime Day成功</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -645,40 +693,40 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 07:25:40 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Update VAT registration information to reinstate Inventory and FBA
  functionality of your Amazon.it store</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -694,39 +742,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 02:44:04 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (y8kVKdPDvp)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -746,39 +794,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:33:15 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
@@ -794,39 +842,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:22:00 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -846,39 +894,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:11 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -898,39 +946,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:21:19 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -947,39 +995,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:07:05 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January-March 2026</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -996,39 +1044,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 14:48:57 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1048,39 +1096,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:42 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -1104,39 +1152,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:19 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -1160,39 +1208,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 13:46:45 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1212,39 +1260,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:49:45 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1264,39 +1312,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:47:51 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1316,39 +1364,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:11:27 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1367,40 +1415,40 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1416,40 +1464,40 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1463,40 +1511,40 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1510,40 +1558,40 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -1556,39 +1604,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -1608,39 +1656,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:06:09 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1655,39 +1703,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 13:00:10 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1702,39 +1750,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 10:15:46 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -1749,39 +1797,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 15:00:47 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1796,39 +1844,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:37 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1843,39 +1891,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:10:53 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -1893,39 +1941,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:55:42 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Ship Smarter: Get 3 FREE Brokerage Fees: Limited Time C2S2 Offer 🚀</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z3hy11/6664114770/h/cIM7P1R6ABFsNRmzeIU2ASpTCxzOevVrUjDi2lts12A)
 Ship Cross-Border &amp; Save Big. Get Started with C2S2 Today.
@@ -1942,39 +1990,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 06:33:16 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1993,39 +2041,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:48:46 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2040,40 +2088,40 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 05:21:00 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -2089,39 +2137,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 17:10:29 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -2134,59 +2182,6 @@
 Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
 Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
 Worten Marketplace tiene una estrategia B2C, c</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 15 May 2026 15:52:25 +0000</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;store-news@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>EchoPlan Magnetic Blocks is still in your cart</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Still thinking about it? https://www.amazon.com/gp/cart/view.html?ref_=cor
-EchoPlan 200PCS Magnetic Blocks, Magnetic Building Blocks, Magnet Blocks Cubes, STEM Educational Stacking Magnet Toy for Kids Ages 3 4 5 6 7 8 9 10 11, Birthday Gifts for Boys and Girls, 1&amp;quot; Large Size
- -42% $34.99 List Price: $59.99
-https://www.amazon.com/gp/product/B0G4CS3GV9/?ref_=
-View Your Cart
-https://www.amazon.com/gp/cart/view.html?ref_=cor
-Check out more options
-Magneverse 200 PCS 0.8in Magnetic Blocks - Magnet Toys for Boys, Magnetic Building Blocks Cubes, Stacking Magnets, School STEM Toys Birthday Gifts for Boys and Girls Age 3+ Years Old (Theme: Portal)
- $45.98
-https://www.amazon.com/gp/product/B0DPZY5X12/?ref_=ci_mcx_mr_2p_0_lm
-Goody King 200 PCS Magnetic Blocks - Forest Magnetic Building Blocks, Stacking Magnets for Kids, Strong Magnets, Sensory Toy for STEM Learning Toys for Kids 3+ Boys and Girls Christmas Birthday Gifts
- $39.99
-https://www.amazon.com/gp/product/B0FBGHLBCK/?ref_=ci_mcx_mr_2p_1_lm
-QBI Magnetic Blocks Play Starter Set – STEM Magnet Building Toys for Kids Ages 3-5, 4-in-1 Race Car Track with 4 Cars &amp;amp; 2 Ramps, Birthday Gift (36 PCS)
- -17% $99.79 List Price: $119.79
-https</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5127,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5147,44 +5142,45 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
+          <t>Fri, 15 May 2026 15:52:25 +0000</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>"Amazon.com" &lt;store-news@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon.com Inventory</t>
+          <t>EchoPlan Magnetic Blocks is still in your cart</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Dear Weihai US,
-You recently received a notice about the removal of your listing(s) for the product(s) listed below.
-You were required to submit a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing within 30 days of the notification sent on 03/21/2026. Since a removal order was not submitted since the notification was sent, we have submitted a disposal order for this inventory in accordance with FBA policies.
-For more information regarding the restriction of this product, see the notification e-mail you received from Product Safety. If you have additional questions, please contact Seller Support.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FD8VC559
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_PRODUCT_REMOVAL_ORDER_CREATED
-SPC-USAmazon-1143494298629858</t>
+          <t>Still thinking about it? https://www.amazon.com/gp/cart/view.html?ref_=cor
+EchoPlan 200PCS Magnetic Blocks, Magnetic Building Blocks, Magnet Blocks Cubes, STEM Educational Stacking Magnet Toy for Kids Ages 3 4 5 6 7 8 9 10 11, Birthday Gifts for Boys and Girls, 1&amp;quot; Large Size
+ -42% $34.99 List Price: $59.99
+https://www.amazon.com/gp/product/B0G4CS3GV9/?ref_=
+View Your Cart
+https://www.amazon.com/gp/cart/view.html?ref_=cor
+Check out more options
+Magneverse 200 PCS 0.8in Magnetic Blocks - Magnet Toys for Boys, Magnetic Building Blocks Cubes, Stacking Magnets, School STEM Toys Birthday Gifts for Boys and Girls Age 3+ Years Old (Theme: Portal)
+ $45.98
+https://www.amazon.com/gp/product/B0DPZY5X12/?ref_=ci_mcx_mr_2p_0_lm
+Goody King 200 PCS Magnetic Blocks - Forest Magnetic Building Blocks, Stacking Magnets for Kids, Strong Magnets, Sensory Toy for STEM Learning Toys for Kids 3+ Boys and Girls Christmas Birthday Gifts
+ $39.99
+https://www.amazon.com/gp/product/B0FBGHLBCK/?ref_=ci_mcx_mr_2p_1_lm
+QBI Magnetic Blocks Play Starter Set – STEM Magnet Building Toys for Kids Ages 3-5, 4-in-1 Race Car Track with 4 Cars &amp;amp; 2 Ramps, Birthday Gift (36 PCS)
+ -17% $99.79 List Price: $119.79
+https</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5199,82 +5195,21 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
+          <t>Thu, 14 May 2026 14:07:42 +0000</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
+          <t>Pagamento elaborato con successo</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>尊敬的卖家/供应商:您好!
-我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
-1) 关于不活跃的商品信息:
-我们已经核实,ASIN: B0FCDRNTT8 目前因化学品安全与合规性 (CSC) 问题而处于不活跃状态。
-您可以在账户健康页面确认此信息:
-https://sellercentral.amazon.com/performance/account/health/product-policies?t=regulatory-compliance
-2) 关于激活商品信息:
-我们看到您已经提交过文件但被拒绝,因此我们建议您重新提交文件。
-请注意,要对"化学品安全与合规性 (CSC)"问题提出申诉,您需要提供详细说明,解释为什么您认为该违规判定是不正确的,并提供支持性文件或证据来支持您的申诉。
-这些证据可能包括发票、真实性证明或其他能够证明您的商品不违反亚马逊商品政策的文件。
-一旦您提交了相关信息,我们的内部团队将审核您的提交并重新激活该商品信息。
-欢迎向亚马逊提交反馈，从而帮助亚马逊改善您的开店体验。
-您对我们提供的支持是否满意？
-如果是，请单击此处
-https://sellercentral.amazon.com/hz/case-dashboard/hmd?p=A3U04I9L0QLTKL&amp;c=20061337331&amp;locale=zh_CN&amp;k=hy
-如果否，请单击此处
-https://sellercentral.amazon.com/hz/case-dashboard/hmd?p=A3U04I9L0QLTKL&amp;c=20061337331&amp;locale=zh_CN&amp;k=hn
-Thank you for selling with Amazon,
-[[Aakash M.]]
-Amazon.com Seller Support
-=======================================
-MORE WAYS TO GET HELP:
-Visit our Seller Forums for help from other sellers: http://sellercentral.amazon.com/forums
-Browse all Seller Help topics: http://sellercentral.amazon.com/gp/help</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 14 May 2026 14:07:42 +0000</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>Pagamento elaborato con successo</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5289,39 +5224,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 03:00:00 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -5351,39 +5286,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 16:40:18 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5411,39 +5346,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:51:48 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -5459,39 +5394,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 10:10:51 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>EPR Pay on Behalf charges for 2024 Amazon.co.uk sales</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5510,39 +5445,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 12:21:34 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -5564,39 +5499,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:22:50 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5618,39 +5553,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -5669,39 +5604,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 08:34:05 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5713,39 +5648,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5757,39 +5692,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -5801,39 +5736,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:29:17 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5845,39 +5780,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:25:39 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5889,39 +5824,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:10:57 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5933,39 +5868,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:09:44 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -5984,39 +5919,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:01:18 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6035,39 +5970,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:25:07 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
@@ -6079,39 +6014,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:24:35 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6123,39 +6058,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:03:04 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6167,39 +6102,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 20:51:50 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6211,39 +6146,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:44:14 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
@@ -6255,39 +6190,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:35:59 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6299,39 +6234,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:24:07 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6343,39 +6278,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:18:06 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6387,39 +6322,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:33:15 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6431,39 +6366,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:20:52 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6475,39 +6410,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:43:38 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6519,39 +6454,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:17:48 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6563,39 +6498,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:52:53 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6607,40 +6542,40 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:40:42 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6659,39 +6594,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:57:28 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6703,39 +6638,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:43:13 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6747,39 +6682,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:40:52 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6791,39 +6726,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:55:06 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6835,39 +6770,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:49:29 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6879,39 +6814,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6932,39 +6867,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6979,39 +6914,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -7030,39 +6965,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 05:32:15 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7084,39 +7019,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Rating Deals</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -7142,40 +7077,40 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -7191,40 +7126,40 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -7240,39 +7175,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -7288,39 +7223,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -7336,39 +7271,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -7384,39 +7319,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -7430,39 +7365,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -7480,40 +7415,40 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -7529,39 +7464,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -7577,39 +7512,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -7625,40 +7560,40 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -7674,39 +7609,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -7723,39 +7658,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -7784,39 +7719,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -7832,39 +7767,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -7878,39 +7813,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7925,39 +7860,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7977,39 +7912,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -8038,40 +7973,40 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -8084,39 +8019,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -8131,39 +8066,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -8176,40 +8111,40 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -8224,40 +8159,40 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -8271,39 +8206,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -8317,39 +8252,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -8364,39 +8299,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -8410,39 +8345,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -8457,39 +8392,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8504,39 +8439,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -8555,39 +8490,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -8603,39 +8538,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -8656,39 +8591,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -8706,40 +8641,40 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -8757,39 +8692,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -8806,39 +8741,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -8856,40 +8791,40 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -8907,39 +8842,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -8957,39 +8892,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -9006,137 +8941,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>Votre paiement est en cours</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Félicitations ! Votre paiement est en cours et arrivera sous peu.
- Tentative de versement
-Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
-Le 04/22/26 15:00 CEST, nous avons effectué un virement d’un montant de €
- 95.42 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
- Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
- Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
- Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de pé</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>Act today &amp; improve Sales on Excess Inventory</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Optional preview text
- Hello,
-We noticed you have a number of ASIN(s) that have excess levels of inventory. We are reaching out to inform you about multiple options to improve your Unit Sales on your aged and/or excess inventory in Amazon Fulfillment Centers. Our goal is to help you increase the sales on this excess inventory:
-X004QEYPRL, X004QEVV05, X004K6ILMZ
-We encourage you to take Amazon recommended actions such as Create Outlet deals, Sponsor Products Ad, to improve sell through of this excess inventory and potentially reduce your chances of incurring aged inventory fee.
- Outlet deals
- Amazon Outlet is a great place for customers to shop for overstock deals, which offers a selection of items, such as electronics, toys, beauty, and kitchen.
- Create Outlet Deal Today!
- Sponsored Product Ads
- Sponsored Products is a cost-per-click advertising solution that provides advertisers with a foundation of controls and visibility to help get their individual products discovered, and help generate sales from traffic sources in the Amazon store and on select premium apps and websites.
- Create Sponsored Products Ad Today!
-We encourage you to vie</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9160,39 +8997,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9215,39 +9052,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9271,39 +9108,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9327,39 +9164,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9380,39 +9217,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
@@ -9421,39 +9258,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -9483,39 +9320,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
